--- a/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/post DFS_HRM-2031-0120/Panel 7/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Back_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-ALPHA-01/30101/BU02/HRM/post DFS_HRM-2031-0120/Panel 7/BACK/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU02_Back_Summary.xlsx
@@ -437,16 +437,6 @@
           <t>Radius</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>Dimple</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Bump</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -460,22 +450,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>16.60411</v>
+        <v>17.13383</v>
       </c>
       <c r="D2" t="n">
-        <v>16.43285</v>
+        <v>16.283</v>
       </c>
       <c r="E2" t="n">
-        <v>16.70875</v>
+        <v>16.63874</v>
       </c>
       <c r="F2" t="n">
-        <v>42.78352</v>
+        <v>42.80576</v>
       </c>
       <c r="G2" t="n">
-        <v>0.04982</v>
+        <v>0.05154</v>
       </c>
       <c r="H2" t="n">
-        <v>1.81594</v>
+        <v>1.7871</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +475,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16.75143</v>
+        <v>16.74002</v>
       </c>
       <c r="D3" t="n">
-        <v>16.62472</v>
+        <v>16.5693</v>
       </c>
       <c r="E3" t="n">
-        <v>16.7297</v>
+        <v>16.57592</v>
       </c>
       <c r="F3" t="n">
-        <v>42.83678</v>
+        <v>42.17055</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05076</v>
+        <v>0.05037</v>
       </c>
       <c r="H3" t="n">
-        <v>1.82321</v>
+        <v>1.81385</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +500,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>16.72487</v>
+        <v>16.78199</v>
       </c>
       <c r="D4" t="n">
-        <v>16.60896</v>
+        <v>16.49631</v>
       </c>
       <c r="E4" t="n">
-        <v>16.76344</v>
+        <v>16.69604</v>
       </c>
       <c r="F4" t="n">
-        <v>43.10346</v>
+        <v>43.26695</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05059</v>
+        <v>0.05125</v>
       </c>
       <c r="H4" t="n">
-        <v>1.81331</v>
+        <v>1.83923</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +525,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.80581</v>
+        <v>16.96764</v>
       </c>
       <c r="D5" t="n">
-        <v>16.97358</v>
+        <v>16.64046</v>
       </c>
       <c r="E5" t="n">
-        <v>16.55129</v>
+        <v>16.86265</v>
       </c>
       <c r="F5" t="n">
-        <v>41.92713</v>
+        <v>43.19234</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05056</v>
+        <v>0.05039</v>
       </c>
       <c r="H5" t="n">
-        <v>1.83679</v>
+        <v>1.84398</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +550,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.72837</v>
+        <v>16.97795</v>
       </c>
       <c r="D6" t="n">
-        <v>16.70231</v>
+        <v>16.27536</v>
       </c>
       <c r="E6" t="n">
-        <v>16.63626</v>
+        <v>16.97107</v>
       </c>
       <c r="F6" t="n">
-        <v>42.06687</v>
+        <v>41.72096</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05048</v>
+        <v>0.05069</v>
       </c>
       <c r="H6" t="n">
-        <v>1.7829</v>
+        <v>1.82734</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +575,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.9268</v>
+        <v>16.83187</v>
       </c>
       <c r="D7" t="n">
-        <v>16.4569</v>
+        <v>16.2301</v>
       </c>
       <c r="E7" t="n">
-        <v>16.80021</v>
+        <v>16.68565</v>
       </c>
       <c r="F7" t="n">
-        <v>42.16135</v>
+        <v>42.36673</v>
       </c>
       <c r="G7" t="n">
-        <v>0.04981</v>
+        <v>0.04992</v>
       </c>
       <c r="H7" t="n">
-        <v>1.82861</v>
+        <v>1.83017</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +600,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.96588</v>
+        <v>17.05736</v>
       </c>
       <c r="D8" t="n">
-        <v>16.45311</v>
+        <v>16.37182</v>
       </c>
       <c r="E8" t="n">
-        <v>16.76608</v>
+        <v>16.8069</v>
       </c>
       <c r="F8" t="n">
-        <v>42.47153</v>
+        <v>42.09682</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05023</v>
+        <v>0.05175</v>
       </c>
       <c r="H8" t="n">
-        <v>1.8204</v>
+        <v>1.83798</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +625,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>16.98146</v>
+        <v>17.23378</v>
       </c>
       <c r="D9" t="n">
-        <v>16.41821</v>
+        <v>16.51361</v>
       </c>
       <c r="E9" t="n">
-        <v>16.71924</v>
+        <v>16.81279</v>
       </c>
       <c r="F9" t="n">
-        <v>42.09731</v>
+        <v>43.21658</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05035</v>
+        <v>0.05163</v>
       </c>
       <c r="H9" t="n">
-        <v>1.81703</v>
+        <v>1.82793</v>
       </c>
     </row>
     <row r="10">
@@ -660,48 +650,33 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>16.655</v>
+        <v>16.97065</v>
       </c>
       <c r="D10" t="n">
-        <v>16.57111</v>
+        <v>16.64291</v>
       </c>
       <c r="E10" t="n">
-        <v>16.53902</v>
+        <v>16.96799</v>
       </c>
       <c r="F10" t="n">
-        <v>42.36204</v>
+        <v>42.14627</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05124</v>
+        <v>0.0508</v>
       </c>
       <c r="H10" t="n">
-        <v>1.85568</v>
+        <v>1.84414</v>
       </c>
     </row>
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>Max Stepheight</t>
+          <t>Dimple</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Min Stepheight</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Mean Stepheight</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Width</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Space</t>
+          <t>Bump</t>
         </is>
       </c>
     </row>
@@ -713,8 +688,14 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Trace 1</t>
-        </is>
+          <t>via 1</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>0.60456</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.12694</v>
       </c>
     </row>
     <row r="13">
@@ -723,6 +704,12 @@
           <t>Unit 8</t>
         </is>
       </c>
+      <c r="C13" t="n">
+        <v>0.62177</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.10096</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -730,6 +717,12 @@
           <t>Unit 9</t>
         </is>
       </c>
+      <c r="C14" t="n">
+        <v>0.6034</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.09653</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -737,6 +730,12 @@
           <t>Unit 4</t>
         </is>
       </c>
+      <c r="C15" t="n">
+        <v>0.60068</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.10237</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -744,6 +743,12 @@
           <t>Unit 5</t>
         </is>
       </c>
+      <c r="C16" t="n">
+        <v>0.61237</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.1056</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -751,6 +756,12 @@
           <t>Unit 6</t>
         </is>
       </c>
+      <c r="C17" t="n">
+        <v>0.59921</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.11556</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -758,6 +769,12 @@
           <t>Unit 1</t>
         </is>
       </c>
+      <c r="C18" t="n">
+        <v>0.61524</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.09452</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -765,12 +782,24 @@
           <t>Unit 2</t>
         </is>
       </c>
+      <c r="C19" t="n">
+        <v>0.59836</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.11143</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
           <t>Unit 3</t>
         </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.6031</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.10968</v>
       </c>
     </row>
   </sheetData>
